--- a/public/data/contract_booking.xlsx
+++ b/public/data/contract_booking.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>8593543f-c9eb-46e1-93f3-a068a721d50a</v>
+        <v>26ee8ef8-d433-40cb-8a0b-c3a941aa7efa</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>8ebd2400-07b1-4c20-a0a9-d4043f893349</v>
+        <v>f5666ed6-33d2-4fbb-a520-2a9f8ff74936</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,108 +470,108 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>a0dce478-fd14-41fb-800f-d3dec166f7e7</v>
+        <v>027fe6a0-6a2b-4055-aa5b-fc0c3ae52b6d</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
-        <v>Advance booking</v>
+        <v>Charter booking</v>
       </c>
       <c r="F4" t="str">
-        <v>48 hours minimum</v>
+        <v>72 hours minimum</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Full manifest required 24h before</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>e48e0eac-3d4a-4982-9910-62e7d868808e</v>
+        <v>4f3f59d8-07d4-4908-838e-4748cce530d6</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
         <v>CTR-002-001</v>
       </c>
       <c r="E5" t="str">
-        <v>Cancellation</v>
+        <v>Advance booking</v>
       </c>
       <c r="F5" t="str">
-        <v>24 hours before departure</v>
+        <v>48 hours minimum</v>
       </c>
       <c r="G5" t="str">
-        <v>100% refund if cancelled 48h prior</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>10157f2e-a3ed-489d-962b-9afd9cf4a0fe</v>
+        <v>28e10377-afe7-4efe-9e56-8d31398ea364</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E6" t="str">
-        <v>Charter booking</v>
+        <v>Cancellation</v>
       </c>
       <c r="F6" t="str">
-        <v>72 hours minimum</v>
+        <v>24 hours before departure</v>
       </c>
       <c r="G6" t="str">
-        <v>Full manifest required 24h before</v>
+        <v>100% refund if cancelled 48h prior</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>93989e2f-cd1a-4832-97fa-24a7d0f84e06</v>
+        <v>912a5ca0-b383-4da3-aa67-8c6577940bbf</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E7" t="str">
-        <v>Advance booking</v>
+        <v>Charter booking</v>
       </c>
       <c r="F7" t="str">
-        <v>48 hours minimum</v>
+        <v>72 hours minimum</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Full manifest required 24h before</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>e4c03a9f-74d0-48de-9e43-93e5afd73067</v>
+        <v>c3d40983-40a5-4e24-ae83-475ff6438939</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E8" t="str">
         <v>Advance booking</v>
@@ -580,159 +580,159 @@
         <v>48 hours minimum</v>
       </c>
       <c r="G8" t="str">
-        <v>Online portal booking available</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>61b9a78e-be4d-4958-aa61-74cb8a612614</v>
+        <v>4e0d4549-e0ad-45f3-b5c0-c72a9085f0c2</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E9" t="str">
-        <v>Cancellation</v>
+        <v>Signed charter booking</v>
       </c>
       <c r="F9" t="str">
-        <v>24 hours before departure</v>
+        <v>96 hours minimum</v>
       </c>
       <c r="G9" t="str">
-        <v>No-show fee: 50% of fare</v>
+        <v>Requires Soneva GM approval</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2ab63d03-e494-4c62-95b4-e1d63eb35778</v>
+        <v>21ec8eae-0ce6-4fa2-9afc-c46d09ff7f7a</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E10" t="str">
-        <v>Amendment</v>
+        <v>Advance booking</v>
       </c>
       <c r="F10" t="str">
-        <v>Free up to 12h before</v>
+        <v>48 hours minimum</v>
       </c>
       <c r="G10" t="str">
-        <v>Name changes $25 per pax</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6612c96e-328e-4b8b-ae31-acc29679a96c</v>
+        <v>d7f571fd-09b7-4159-811a-86794b13b5dd</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E11" t="str">
-        <v>Advance booking</v>
+        <v>Charter booking</v>
       </c>
       <c r="F11" t="str">
-        <v>24 hours minimum</v>
+        <v>72 hours minimum</v>
       </c>
       <c r="G11" t="str">
-        <v>Speedboat more flexible</v>
+        <v>Marriott group coordination</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>50a8531d-de10-4afa-a428-1dec98e7de28</v>
+        <v>7711da02-8693-477c-a552-66c40ea5239d</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E12" t="str">
-        <v>Charter booking</v>
+        <v>Advance booking</v>
       </c>
       <c r="F12" t="str">
-        <v>72 hours minimum</v>
+        <v>48 hours minimum</v>
       </c>
       <c r="G12" t="str">
-        <v>Full pax manifest 48h before</v>
+        <v>Online portal booking available</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>b7e3d11d-1d71-4ec2-afdd-80dac4fe9723</v>
+        <v>f73df0c9-3d99-40eb-98f0-08febf5a87e8</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E13" t="str">
         <v>Cancellation</v>
       </c>
       <c r="F13" t="str">
-        <v>48 hours before departure</v>
+        <v>24 hours before departure</v>
       </c>
       <c r="G13" t="str">
-        <v>50% penalty for late cancel</v>
+        <v>No-show fee: 50% of fare</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>258c59be-9358-4b2d-af5c-39b850385805</v>
+        <v>e15739d9-7399-4508-a6e2-0a49ceeebe25</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E14" t="str">
-        <v>Advance booking</v>
+        <v>Amendment</v>
       </c>
       <c r="F14" t="str">
-        <v>24 hours minimum</v>
+        <v>Free up to 12h before</v>
       </c>
       <c r="G14" t="str">
-        <v>Speedboat schedule</v>
+        <v>Name changes $25 per pax</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>d85540d9-3e49-43a0-8435-fcbee8d478d6</v>
+        <v>1528b98f-cc21-4958-8fef-75c3637b81d5</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D15" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-006-002</v>
       </c>
       <c r="E15" t="str">
         <v>Charter booking</v>
@@ -741,12 +741,219 @@
         <v>72 hours minimum</v>
       </c>
       <c r="G15" t="str">
+        <v>Full manifest 48h before</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>055f1d09-38b7-44ec-989d-4151b343353e</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Signed charter booking</v>
+      </c>
+      <c r="F16" t="str">
+        <v>96 hours minimum</v>
+      </c>
+      <c r="G16" t="str">
+        <v>FS Regional approval required</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3eb2d448-9ed1-40fc-b979-df7ab9315c2c</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Advance booking</v>
+      </c>
+      <c r="F17" t="str">
+        <v>24 hours minimum</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Speedboat more flexible</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9d659a3d-6add-4444-94b3-f62dbac29d5e</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Advance booking</v>
+      </c>
+      <c r="F18" t="str">
+        <v>48 hours minimum</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Seaplane requires more notice</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4a390d7d-80a3-400d-a386-67e3a7b4d3b5</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Charter booking</v>
+      </c>
+      <c r="F19" t="str">
+        <v>72 hours minimum</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Full pax manifest 48h before</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>6c83ee1b-02f2-4f6b-bafa-09c5be73731f</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Cancellation</v>
+      </c>
+      <c r="F20" t="str">
+        <v>48 hours before departure</v>
+      </c>
+      <c r="G20" t="str">
+        <v>50% penalty for late cancel</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>dad4d58c-f73b-4f28-9fb4-390d2c7a59da</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Advance booking</v>
+      </c>
+      <c r="F21" t="str">
+        <v>48 hours minimum</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>57308cbc-eba8-435b-9af6-d86f3ec60ccd</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Advance booking</v>
+      </c>
+      <c r="F22" t="str">
+        <v>24 hours minimum</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Speedboat schedule</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>f3fad190-ac88-4191-a358-1face13fc55f</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Charter booking</v>
+      </c>
+      <c r="F23" t="str">
+        <v>72 hours minimum</v>
+      </c>
+      <c r="G23" t="str">
         <v>Soneva concierge handles</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>eee1bbd0-5680-4c21-bf5f-a8fa1403949b</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Advance booking</v>
+      </c>
+      <c r="F24" t="str">
+        <v>48 hours minimum</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G24"/>
   </ignoredErrors>
 </worksheet>
 </file>